--- a/stories/arbres/ATOM-EMO.LEX.006-03.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.006-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Noémie est dans le salon. Dehors, le vent pousse un volet. Le volet claque. Noémie sent son ventre se serrer. Elle dit : je suis inquiète. Elle va vers maman. Maman est l'adulte près de la table. Noémie raconte : le volet a fait un grand bruit. Maman écoute. Maman dit : tu as su raconter. Papa ferme le volet. Le salon redevient calme. Plus tard, Noémie va au jardin avec papa. Un oiseau s'envole tout près. Le ventre de Noémie se serre encore. Noémie se souvient. Elle va vers papa. Papa est l'adulte. Elle dit : je suis inquiète. Elle raconte l'oiseau. Papa écoute. Noémie souffle. Son ventre se desserre un peu. Être inquiet, on peut le dire. On va vers un adulte. On peut raconter. Noémie a transféré le geste : ventre serré, adulte, raconter.</t>
+          <t>Noémie est dans le salon. Dehors, le vent pousse un volet. Le volet claque. Noémie sent son ventre se serrer. Je suis inquiète. Elle va vers maman. Maman est l'adulte près de la table. Noémie raconte : le volet a fait un grand bruit. Maman écoute. Tu as su raconter. Papa ferme le volet. Le salon redevient calme. Plus tard, Noémie va au jardin avec papa. Un oiseau s'envole tout près. Le ventre de Noémie se serre encore. Noémie se souvient. Elle va vers papa. Papa est l'adulte. Je suis inquiète. Elle raconte l'oiseau. Papa écoute. Noémie souffle. Son ventre se desserre un peu. Être inquiet, on peut le dire. On va vers un adulte. On peut raconter. Noémie a transféré le geste : ventre serré, adulte, raconter.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Noémie est dans le salon. Dehors, le vent pousse un volet. Le volet claque. Noémie sent son ventre se serrer.
+narrateur|Je suis inquiète. Elle va vers maman. Maman est l'adulte près de la table.
+narrateur|Noémie raconte : le volet a fait un grand bruit. Maman écoute.
+maman|Tu as su raconter. Papa ferme le volet.
+narrateur|Le salon redevient calme. Plus tard, Noémie va au jardin avec papa. Un oiseau s'envole tout près. Le ventre de Noémie se serre encore. Noémie se souvient. Elle va vers papa. Papa est l'adulte.
+narrateur|Je suis inquiète. Elle raconte l'oiseau. Papa écoute.
+narrateur|Noémie souffle. Son ventre se desserre un peu. Être inquiet, on peut le dire. On va vers un adulte. On peut raconter. Noémie a transféré le geste : ventre serré, adulte, raconter.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Noémie a le ventre serré. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Noémie a nommé : inquiet. Elle a rejoint un adulte. Elle a pu raconter. Au salon, puis au jardin.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1832,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Noémie cueille une feuille. Papa tient sa main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1999,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2039,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.006-03.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.006-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Noémie souffle. Son ventre se desserre un peu. Être inquiet, on peut le dire. On va vers un adulte. On peut raconter. Noémie a transféré le geste : ventre serré, adulte, raconter.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Noémie a le ventre serré. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1677,7 @@
           <t>narrateur|Noémie a nommé : inquiet. Elle a rejoint un adulte. Elle a pu raconter. Au salon, puis au jardin.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1845,7 @@
           <t>narrateur|Noémie cueille une feuille. Papa tient sa main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2004,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2247,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.006-03.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.006-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Noémie raconte qu'elle est inquiète</t>
+          <t>Sarah raconte son inquiétude</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,7 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +831,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un volet claque. Sarah a le ventre serré. Elle raconte à maman. Au jardin, un oiseau s'envole. Elle reprend le geste avec papa.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1185,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Noémie est dans le salon. Dehors, le vent pousse un volet. Le volet claque. Noémie sent son ventre se serrer. Je suis inquiète. Elle va vers maman. Maman est l'adulte près de la table. Noémie raconte : le volet a fait un grand bruit. Maman écoute. Tu as su raconter. Papa ferme le volet. Le salon redevient calme. Plus tard, Noémie va au jardin avec papa. Un oiseau s'envole tout près. Le ventre de Noémie se serre encore. Noémie se souvient. Elle va vers papa. Papa est l'adulte. Je suis inquiète. Elle raconte l'oiseau. Papa écoute. Noémie souffle. Son ventre se desserre un peu. Être inquiet, on peut le dire. On va vers un adulte. On peut raconter. Noémie a transféré le geste : ventre serré, adulte, raconter.</t>
+          <t>Le pull de laine attend sur la chaise. Il sent encore le savon. Dans la cheminée, le vent chuchote. Un tout petit air, comme une flûte. Sur la table, une tasse a laissé un rond. Le rond est encore un peu chaud. Un fil de laine pend du pull. Il est beige, tout doux. Sarah, tu veux ton pull ? Oui, maman. Il est doux. Le vent est là, dehors. En ce moment, Sarah est dans le salon. Dehors, le vent pousse un volet. Le volet claque. Sarah sent son ventre se serrer. Ses mains deviennent froides. Je suis inquiète. Elle va vers maman. Maman est l'adulte près de la table. J'ai le ventre serré. Le volet a fait un grand bruit. Tu peux raconter. Je t'écoute, Sarah. Être inquiète, ce n'est pas honteux. Sarah raconte le bruit du volet. Le pull de laine est chaud sur ses épaules. Tu as su raconter. Bravo, Sarah. Je ferme le volet. Le salon redevient calme. Tu as dit : je suis inquiète. Tu es venue vers un adulte. Tu as fait du bon travail. Sarah souffle. Son ventre se desserre un peu. Plus tard, Sarah va au jardin avec papa. L'herbe est un peu froide. Une feuille sèche craque sous le pied. Un oiseau s'envole tout près. Le ventre de Sarah se serre encore. Ses mains redeviennent froides. Sarah se souvient. Elle va vers papa. Papa est l'adulte. Je suis inquiète. L'oiseau est parti tout vite. Tu peux raconter. Sarah raconte l'oiseau. Une feuille sèche craque encore. Merci d'avoir dit. Tu as repris le geste. Au salon, puis au jardin. Bravo. Sarah souffle. Son ventre se desserre un peu. Être inquiet, on peut le dire. On va vers un adulte. On peut raconter.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1325,72 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Noémie est dans le salon. Dehors, le vent pousse un volet. Le volet claque. Noémie sent son ventre se serrer.
-narrateur|Je suis inquiète. Elle va vers maman. Maman est l'adulte près de la table.
-narrateur|Noémie raconte : le volet a fait un grand bruit. Maman écoute.
-maman|Tu as su raconter. Papa ferme le volet.
-narrateur|Le salon redevient calme. Plus tard, Noémie va au jardin avec papa. Un oiseau s'envole tout près. Le ventre de Noémie se serre encore. Noémie se souvient. Elle va vers papa. Papa est l'adulte.
-narrateur|Je suis inquiète. Elle raconte l'oiseau. Papa écoute.
-narrateur|Noémie souffle. Son ventre se desserre un peu. Être inquiet, on peut le dire. On va vers un adulte. On peut raconter. Noémie a transféré le geste : ventre serré, adulte, raconter.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Le pull de laine attend sur la chaise.
+narrateur|Il sent encore le savon.
+narrateur|Dans la cheminée, le vent chuchote.
+narrateur|Un tout petit air, comme une flûte.
+narrateur|Sur la table, une tasse a laissé un rond.
+narrateur|Le rond est encore un peu chaud.
+narrateur|Un fil de laine pend du pull.
+narrateur|Il est beige, tout doux.
+maman|Sarah, tu veux ton pull ?
+enfant-f|Oui, maman.
+enfant-f|Il est doux.
+papa|Le vent est là, dehors.
+narrateur|En ce moment, Sarah est dans le salon.
+narrateur|Dehors, le vent pousse un volet.
+narrateur|Le volet claque.
+narrateur|Sarah sent son ventre se serrer.
+narrateur|Ses mains deviennent froides.
+enfant-f|Je suis inquiète.
+narrateur|Elle va vers maman.
+narrateur|Maman est l'adulte près de la table.
+enfant-f|J'ai le ventre serré.
+enfant-f|Le volet a fait un grand bruit.
+maman|Tu peux raconter.
+maman|Je t'écoute, Sarah.
+maman|Être inquiète, ce n'est pas honteux.
+narrateur|Sarah raconte le bruit du volet.
+narrateur|Le pull de laine est chaud sur ses épaules.
+maman|Tu as su raconter.
+maman|Bravo, Sarah.
+papa|Je ferme le volet.
+narrateur|Le salon redevient calme.
+papa|Tu as dit : je suis inquiète.
+papa|Tu es venue vers un adulte.
+papa|Tu as fait du bon travail.
+narrateur|Sarah souffle.
+narrateur|Son ventre se desserre un peu.
+narrateur|Plus tard, Sarah va au jardin avec papa.
+narrateur|L'herbe est un peu froide.
+narrateur|Une feuille sèche craque sous le pied.
+narrateur|Un oiseau s'envole tout près.
+narrateur|Le ventre de Sarah se serre encore.
+narrateur|Ses mains redeviennent froides.
+narrateur|Sarah se souvient.
+narrateur|Elle va vers papa.
+narrateur|Papa est l'adulte.
+enfant-f|Je suis inquiète.
+enfant-f|L'oiseau est parti tout vite.
+papa|Tu peux raconter.
+narrateur|Sarah raconte l'oiseau.
+narrateur|Une feuille sèche craque encore.
+papa|Merci d'avoir dit.
+papa|Tu as repris le geste.
+papa|Au salon, puis au jardin.
+papa|Bravo.
+narrateur|Sarah souffle.
+narrateur|Son ventre se desserre un peu.
+narrateur|Être inquiet, on peut le dire.
+narrateur|On va vers un adulte.
+narrateur|On peut raconter.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>vent</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,7 +1415,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Noémie a le ventre serré. Que fait-elle ?</t>
+          <t>Sarah a le ventre serré. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1571,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Noémie a le ventre serré. Que fait-elle ?</t>
+          <t>narrateur|Sarah a le ventre serré.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1600,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Noémie a nommé : inquiet. Elle a rejoint un adulte. Elle a pu raconter. Au salon, puis au jardin.</t>
+          <t>Sarah a nommé : inquiète. Elle a rejoint un adulte. Elle a pu raconter. Au salon, puis au jardin. Je suis inquiète. Tu as raconté le volet. Et l'oiseau, aussi. Bravo, Sarah. Tu as fait du bon travail. Mon ventre est moins serré. Le pull de laine est sur ses épaules. Il sent encore le savon.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,7 +1744,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Noémie a nommé : inquiet. Elle a rejoint un adulte. Elle a pu raconter. Au salon, puis au jardin.</t>
+          <t>narrateur|Sarah a nommé : inquiète.
+narrateur|Elle a rejoint un adulte.
+narrateur|Elle a pu raconter.
+narrateur|Au salon, puis au jardin.
+enfant-f|Je suis inquiète.
+maman|Tu as raconté le volet.
+papa|Et l'oiseau, aussi.
+papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+enfant-f|Mon ventre est moins serré.
+narrateur|Le pull de laine est sur ses épaules.
+narrateur|Il sent encore le savon.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1702,7 +1783,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Noémie cueille une feuille. Papa tient sa main.</t>
+          <t>Sarah cueille une feuille. Papa tient sa main. La feuille est sèche, tu vois ? Elle craque un peu. On rentre quand tu veux. Encore un moment. Tu as raconté deux fois. C'est du bon travail. Le jardin est plus calme. L'oiseau est dans l'arbre, plus loin. Le volet ne claque plus. Le vent chuchote encore, tout bas.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,10 +1923,25 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Noémie cueille une feuille. Papa tient sa main.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Sarah cueille une feuille.
+narrateur|Papa tient sa main.
+papa|La feuille est sèche, tu vois ?
+enfant-f|Elle craque un peu.
+maman|On rentre quand tu veux.
+enfant-f|Encore un moment.
+papa|Tu as raconté deux fois.
+papa|C'est du bon travail.
+enfant-f|Le jardin est plus calme.
+maman|L'oiseau est dans l'arbre, plus loin.
+narrateur|Le volet ne claque plus.
+narrateur|Le vent chuchote encore, tout bas.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1870,7 +1966,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai dit : je suis inquiète. J'ai raconté à maman, et à papa. Être inquiète, on peut le dire. Bravo, Sarah. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,7 +2106,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai dit : je suis inquiète.
+enfant-f|J'ai raconté à maman, et à papa.
+maman|Être inquiète, on peut le dire.
+papa|Bravo, Sarah.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2032,7 +2132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2170,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.006-03.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.006-03.xlsx
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le pull de laine attend sur la chaise. Il sent encore le savon. Dans la cheminée, le vent chuchote. Un tout petit air, comme une flûte. Sur la table, une tasse a laissé un rond. Le rond est encore un peu chaud. Un fil de laine pend du pull. Il est beige, tout doux. Sarah, tu veux ton pull ? Oui, maman. Il est doux. Le vent est là, dehors. En ce moment, Sarah est dans le salon. Dehors, le vent pousse un volet. Le volet claque. Sarah sent son ventre se serrer. Ses mains deviennent froides. Je suis inquiète. Elle va vers maman. Maman est l'adulte près de la table. J'ai le ventre serré. Le volet a fait un grand bruit. Tu peux raconter. Je t'écoute, Sarah. Être inquiète, ce n'est pas honteux. Sarah raconte le bruit du volet. Le pull de laine est chaud sur ses épaules. Tu as su raconter. Bravo, Sarah. Je ferme le volet. Le salon redevient calme. Tu as dit : je suis inquiète. Tu es venue vers un adulte. Tu as fait du bon travail. Sarah souffle. Son ventre se desserre un peu. Plus tard, Sarah va au jardin avec papa. L'herbe est un peu froide. Une feuille sèche craque sous le pied. Un oiseau s'envole tout près. Le ventre de Sarah se serre encore. Ses mains redeviennent froides. Sarah se souvient. Elle va vers papa. Papa est l'adulte. Je suis inquiète. L'oiseau est parti tout vite. Tu peux raconter. Sarah raconte l'oiseau. Une feuille sèche craque encore. Merci d'avoir dit. Tu as repris le geste. Au salon, puis au jardin. Bravo. Sarah souffle. Son ventre se desserre un peu. Être inquiet, on peut le dire. On va vers un adulte. On peut raconter.</t>
+          <t>Le pull de laine attend sur la chaise. Il sent encore le savon. Dans la cheminée, le vent chuchote. Un tout petit air, comme une flûte. Sur la table, une tasse a laissé un rond. Le rond est encore un peu chaud. Un fil de laine pend du pull. Il est beige, tout doux. Sarah, tu veux ton pull ? Oui, maman. Il est doux. Le vent est là, dehors. En ce moment, Sarah est dans le salon. Dehors, le vent pousse un volet. Le volet claque. Sarah sent son ventre se serrer. Ses mains deviennent froides. Je suis inquiète. Elle va vers maman. Maman est l'adulte près de la table. J'ai le ventre serré. Le volet a fait un grand bruit. Tu peux raconter. Je t'écoute, Sarah. Être inquiète, ce n'est pas honteux. Sarah raconte le bruit du volet. Le pull de laine est chaud sur ses épaules. Tu as su raconter. Bravo, Sarah. Je ferme le volet. Le salon redevient calme. Tu as dit : je suis inquiète. Tu es venue vers un adulte. Sarah souffle. Son ventre se desserre un peu. Plus tard, Sarah va au jardin avec papa. L'herbe est un peu froide. Une feuille sèche craque sous le pied. Un oiseau s'envole tout près. Le ventre de Sarah se serre encore. Ses mains redeviennent froides. Sarah se souvient. Elle va vers papa. Papa est l'adulte. Je suis inquiète. L'oiseau est parti tout vite. Tu peux raconter. Sarah raconte l'oiseau. Une feuille sèche craque encore. Merci d'avoir dit. Tu as repris le geste. Au salon, puis au jardin. Bravo. Sarah souffle. Son ventre se desserre un peu. Être inquiet, on peut le dire. On va vers un adulte. On peut raconter.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Noémie est dans le salon. Dehors, le vent pousse un volet. Le volet claque. Noémie sent son ventre se serrer. Elle dit : je suis inquiète. Elle va vers maman. Maman est l'adulte près de la table. Noémie raconte : le volet a fait un grand bruit. Maman écoute. Maman dit : tu as su raconter. Papa ferme le volet. Le salon redevient calme. Plus tard, Noémie va au jardin avec papa. Un oiseau s'envole tout près. Le ventre de Noémie se serre encore. Noémie se souvient. Elle va vers papa. Papa est l'adulte. Elle dit : je suis inquiète. Elle raconte l'oiseau. Papa écoute. Noémie souffle. Son ventre se desserre un peu. Être &lt;emphasis level="moderate"&gt;inquiet&lt;/emphasis&gt;, on peut le dire. On va vers un adulte. On peut raconter. Noémie a transféré le geste : ventre serré, adulte, raconter.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le pull de laine attend sur la chaise. Il sent encore le savon. Dans la cheminée, le vent chuchote. Un tout petit air, comme une flûte. Sur la table, une tasse a laissé un rond. Le rond est encore un peu chaud. Un fil de laine pend du pull. Il est beige, tout doux. Sarah, tu veux ton pull ? Oui, maman. Il est doux. Le vent est là, dehors. En ce moment, Sarah est dans le salon. Dehors, le vent pousse un volet. Le volet claque. Sarah sent son ventre se serrer. Ses mains deviennent froides. Je suis inquiète. Elle va vers maman. Maman est l'adulte près de la table. J'ai le ventre serré. Le volet a fait un grand bruit. Tu peux raconter. Je t'écoute, Sarah. Être inquiète, ce n'est pas honteux. Sarah raconte le bruit du volet. Le pull de laine est chaud sur ses épaules. Tu as su raconter. Bravo, Sarah. Je ferme le volet. Le salon redevient calme. Tu as dit : je suis inquiète. Tu es venue vers un adulte. Sarah souffle. Son ventre se desserre un peu. Plus tard, Sarah va au jardin avec papa. L'herbe est un peu froide. Une feuille sèche craque sous le pied. Un oiseau s'envole tout près. Le ventre de Sarah se serre encore. Ses mains redeviennent froides. Sarah se souvient. Elle va vers papa. Papa est l'adulte. Je suis inquiète. L'oiseau est parti tout vite. Tu peux raconter. Sarah raconte l'oiseau. Une feuille sèche craque encore. Merci d'avoir dit. Tu as repris le geste. Au salon, puis au jardin. Bravo. Sarah souffle. Son ventre se desserre un peu. Être inquiet, on peut le dire. On va vers un adulte. On peut raconter.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1358,7 +1358,6 @@
 narrateur|Le salon redevient calme.
 papa|Tu as dit : je suis inquiète.
 papa|Tu es venue vers un adulte.
-papa|Tu as fait du bon travail.
 narrateur|Sarah souffle.
 narrateur|Son ventre se desserre un peu.
 narrateur|Plus tard, Sarah va au jardin avec papa.
@@ -1420,7 +1419,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Noémie a le ventre serré. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah a le ventre serré. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1575,7 +1574,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1600,12 +1598,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sarah a nommé : inquiète. Elle a rejoint un adulte. Elle a pu raconter. Au salon, puis au jardin. Je suis inquiète. Tu as raconté le volet. Et l'oiseau, aussi. Bravo, Sarah. Tu as fait du bon travail. Mon ventre est moins serré. Le pull de laine est sur ses épaules. Il sent encore le savon.</t>
+          <t>Sarah a nommé : inquiète. Elle a rejoint un adulte. Elle a pu raconter. Au salon, puis au jardin. Je suis inquiète. Tu as raconté le volet. Et l'oiseau, aussi. Bravo, Sarah. Mon ventre est moins serré. Le pull de laine est sur ses épaules. Il sent encore le savon.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Noémie a nommé : &lt;emphasis level="moderate"&gt;inquiet&lt;/emphasis&gt;. Elle a rejoint un adulte. Elle a pu raconter. Au salon, puis au jardin.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah a nommé : inquiète. Elle a rejoint un adulte. Elle a pu raconter. Au salon, puis au jardin. Je suis inquiète. Tu as raconté le volet. Et l'oiseau, aussi. Bravo, Sarah. Mon ventre est moins serré. Le pull de laine est sur ses épaules. Il sent encore le savon.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1752,13 +1750,11 @@
 maman|Tu as raconté le volet.
 papa|Et l'oiseau, aussi.
 papa|Bravo, Sarah.
-papa|Tu as fait du bon travail.
 enfant-f|Mon ventre est moins serré.
 narrateur|Le pull de laine est sur ses épaules.
 narrateur|Il sent encore le savon.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1783,12 +1779,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Sarah cueille une feuille. Papa tient sa main. La feuille est sèche, tu vois ? Elle craque un peu. On rentre quand tu veux. Encore un moment. Tu as raconté deux fois. C'est du bon travail. Le jardin est plus calme. L'oiseau est dans l'arbre, plus loin. Le volet ne claque plus. Le vent chuchote encore, tout bas.</t>
+          <t>Sarah cueille une feuille. Papa tient sa main. La feuille est sèche, tu vois ? Elle craque un peu. On rentre quand tu veux. Encore un moment. Tu as raconté deux fois. Le jardin est plus calme. L'oiseau est dans l'arbre, plus loin. Le volet ne claque plus. Le vent chuchote encore, tout bas.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Noémie cueille une feuille. Papa tient sa &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah cueille une feuille. Papa tient sa main. La feuille est sèche, tu vois ? Elle craque un peu. On rentre quand tu veux. Encore un moment. Tu as raconté deux fois. Le jardin est plus calme. L'oiseau est dans l'arbre, plus loin. Le volet ne claque plus. Le vent chuchote encore, tout bas.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1930,7 +1926,6 @@
 maman|On rentre quand tu veux.
 enfant-f|Encore un moment.
 papa|Tu as raconté deux fois.
-papa|C'est du bon travail.
 enfant-f|Le jardin est plus calme.
 maman|L'oiseau est dans l'arbre, plus loin.
 narrateur|Le volet ne claque plus.
@@ -1966,12 +1961,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit : je suis inquiète. J'ai raconté à maman, et à papa. Être inquiète, on peut le dire. Bravo, Sarah. L'histoire est finie.</t>
+          <t>J'ai dit : je suis inquiète. J'ai raconté à maman, et à papa. Être inquiète, on peut le dire. Bravo, Sarah.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai dit : je suis inquiète. J'ai raconté à maman, et à papa. Être inquiète, on peut le dire. Bravo, Sarah.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2109,11 +2104,9 @@
           <t>enfant-f|J'ai dit : je suis inquiète.
 enfant-f|J'ai raconté à maman, et à papa.
 maman|Être inquiète, on peut le dire.
-papa|Bravo, Sarah.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+papa|Bravo, Sarah.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2132,7 +2125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2177,6 +2170,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.006-03.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.006-03.xlsx
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -684,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Noémie, maman, papa</t>
+          <t>Sarah, maman, papa</t>
         </is>
       </c>
     </row>
